--- a/Data/pending.xlsx
+++ b/Data/pending.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python_dev\item_cost_update\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Item_Cost_update\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A58F567-57D1-4B7B-86B0-EB057FB8D7FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E06ABD-DF25-483A-95A2-9EBB7F266AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="645" yWindow="1530" windowWidth="21600" windowHeight="11385" xr2:uid="{6D65B06D-4D01-4435-B64D-A9555991AFEA}"/>
+    <workbookView xWindow="9195" yWindow="5190" windowWidth="14595" windowHeight="10455" xr2:uid="{6D65B06D-4D01-4435-B64D-A9555991AFEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,606 +35,480 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="200">
-  <si>
-    <t>Annual</t>
-  </si>
-  <si>
-    <t>18965464-005</t>
-  </si>
-  <si>
-    <t>18965464-011</t>
-  </si>
-  <si>
-    <t>18966575-012</t>
-  </si>
-  <si>
-    <t>18992953-002</t>
-  </si>
-  <si>
-    <t>19022667-001</t>
-  </si>
-  <si>
-    <t>18912883-001</t>
-  </si>
-  <si>
-    <t>10360352-001</t>
-  </si>
-  <si>
-    <t>11438724-001</t>
-  </si>
-  <si>
-    <t>11470253-001</t>
-  </si>
-  <si>
-    <t>10450244-001</t>
-  </si>
-  <si>
-    <t>16531533-001</t>
-  </si>
-  <si>
-    <t>16718668-001</t>
-  </si>
-  <si>
-    <t>17975233-001</t>
-  </si>
-  <si>
-    <t>10492537-145</t>
-  </si>
-  <si>
-    <t>11106484-003</t>
-  </si>
-  <si>
-    <t>11106484-004</t>
-  </si>
-  <si>
-    <t>11106484-005</t>
-  </si>
-  <si>
-    <t>18259800-001</t>
-  </si>
-  <si>
-    <t>18716688-038</t>
-  </si>
-  <si>
-    <t>18716688-039</t>
-  </si>
-  <si>
-    <t>18716688-041</t>
-  </si>
-  <si>
-    <t>18782219-002</t>
-  </si>
-  <si>
-    <t>18782219-005</t>
-  </si>
-  <si>
-    <t>18782219-006</t>
-  </si>
-  <si>
-    <t>18782219-007</t>
-  </si>
-  <si>
-    <t>18786796-001</t>
-  </si>
-  <si>
-    <t>18849246-001</t>
-  </si>
-  <si>
-    <t>18734536-001</t>
-  </si>
-  <si>
-    <t>11374042-001</t>
-  </si>
-  <si>
-    <t>16547273-026</t>
-  </si>
-  <si>
-    <t>16702487-001</t>
-  </si>
-  <si>
-    <t>18715108-013</t>
-  </si>
-  <si>
-    <t>18731781-001</t>
-  </si>
-  <si>
-    <t>18738593-003</t>
-  </si>
-  <si>
-    <t>18738939-011</t>
-  </si>
-  <si>
-    <t>18738978-011</t>
-  </si>
-  <si>
-    <t>18746748-001</t>
-  </si>
-  <si>
-    <t>18749850-007</t>
-  </si>
-  <si>
-    <t>18749876-006</t>
-  </si>
-  <si>
-    <t>18750313-003</t>
-  </si>
-  <si>
-    <t>18750317-004</t>
-  </si>
-  <si>
-    <t>18831482-001</t>
-  </si>
-  <si>
-    <t>18831482-002</t>
-  </si>
-  <si>
-    <t>18867515-007</t>
-  </si>
-  <si>
-    <t>18875709-001</t>
-  </si>
-  <si>
-    <t>18918252-001</t>
-  </si>
-  <si>
-    <t>18921520-001</t>
-  </si>
-  <si>
-    <t>18927420-002</t>
-  </si>
-  <si>
-    <t>18953408-052</t>
-  </si>
-  <si>
-    <t>18953408-053</t>
-  </si>
-  <si>
-    <t>18965464-009</t>
-  </si>
-  <si>
-    <t>18967076-002</t>
-  </si>
-  <si>
-    <t>18971923-001</t>
-  </si>
-  <si>
-    <t>17873274-032</t>
-  </si>
-  <si>
-    <t>18312797-025</t>
-  </si>
-  <si>
-    <t>18312797-026</t>
-  </si>
-  <si>
-    <t>18644042-001</t>
-  </si>
-  <si>
-    <t>18907508-005</t>
-  </si>
-  <si>
-    <t>18953408-054</t>
-  </si>
-  <si>
-    <t>18953408-055</t>
-  </si>
-  <si>
-    <t>18953408-056</t>
-  </si>
-  <si>
-    <t>18953408-057</t>
-  </si>
-  <si>
-    <t>18953408-058</t>
-  </si>
-  <si>
-    <t>18953408-059</t>
-  </si>
-  <si>
-    <t>18953408-060</t>
-  </si>
-  <si>
-    <t>18953408-061</t>
-  </si>
-  <si>
-    <t>18953408-062</t>
-  </si>
-  <si>
-    <t>18953408-063</t>
-  </si>
-  <si>
-    <t>18953408-064</t>
-  </si>
-  <si>
-    <t>18953408-065</t>
-  </si>
-  <si>
-    <t>18953408-066</t>
-  </si>
-  <si>
-    <t>18953408-067</t>
-  </si>
-  <si>
-    <t>18953408-068</t>
-  </si>
-  <si>
-    <t>18953408-069</t>
-  </si>
-  <si>
-    <t>18953408-070</t>
-  </si>
-  <si>
-    <t>18953408-071</t>
-  </si>
-  <si>
-    <t>18953408-072</t>
-  </si>
-  <si>
-    <t>18953408-073</t>
-  </si>
-  <si>
-    <t>18953408-074</t>
-  </si>
-  <si>
-    <t>18953408-075</t>
-  </si>
-  <si>
-    <t>18953408-076</t>
-  </si>
-  <si>
-    <t>18953408-077</t>
-  </si>
-  <si>
-    <t>18609525-049</t>
-  </si>
-  <si>
-    <t>18645213-337</t>
-  </si>
-  <si>
-    <t>18656145-014</t>
-  </si>
-  <si>
-    <t>18701901-001</t>
-  </si>
-  <si>
-    <t>18739317-001</t>
-  </si>
-  <si>
-    <t>18751231-008</t>
-  </si>
-  <si>
-    <t>18904524-001</t>
-  </si>
-  <si>
-    <t>18950988-001</t>
-  </si>
-  <si>
-    <t>18962987-001</t>
-  </si>
-  <si>
-    <t>18962992-001</t>
-  </si>
-  <si>
-    <t>18992113-001</t>
-  </si>
-  <si>
-    <t>11364497-001</t>
-  </si>
-  <si>
-    <t>18718097-001</t>
-  </si>
-  <si>
-    <t>18870042-001</t>
-  </si>
-  <si>
-    <t>18759996-028</t>
-  </si>
-  <si>
-    <t>16119619-001</t>
-  </si>
-  <si>
-    <t>18593287-001</t>
-  </si>
-  <si>
-    <t>18597873-001</t>
-  </si>
-  <si>
-    <t>18835463-001</t>
-  </si>
-  <si>
-    <t>18913564-001</t>
-  </si>
-  <si>
-    <t>17865132-001</t>
-  </si>
-  <si>
-    <t>17865133-001</t>
-  </si>
-  <si>
-    <t>18868595-001</t>
-  </si>
-  <si>
-    <t>18645213-391</t>
-  </si>
-  <si>
-    <t>18645213-392</t>
-  </si>
-  <si>
-    <t>18645213-393</t>
-  </si>
-  <si>
-    <t>18645213-394</t>
-  </si>
-  <si>
-    <t>18645213-395</t>
-  </si>
-  <si>
-    <t>18645213-396</t>
-  </si>
-  <si>
-    <t>18645213-397</t>
-  </si>
-  <si>
-    <t>18645213-398</t>
-  </si>
-  <si>
-    <t>18686710-005</t>
-  </si>
-  <si>
-    <t>18906387-001</t>
-  </si>
-  <si>
-    <t>18973603-001</t>
-  </si>
-  <si>
-    <t>10679758-001</t>
-  </si>
-  <si>
-    <t>17777546-005</t>
-  </si>
-  <si>
-    <t>18253156-076</t>
-  </si>
-  <si>
-    <t>18453840-034</t>
-  </si>
-  <si>
-    <t>18562131-018</t>
-  </si>
-  <si>
-    <t>18562131-019</t>
-  </si>
-  <si>
-    <t>18562131-020</t>
-  </si>
-  <si>
-    <t>18562131-021</t>
-  </si>
-  <si>
-    <t>18562131-022</t>
-  </si>
-  <si>
-    <t>18562131-023</t>
-  </si>
-  <si>
-    <t>18562131-024</t>
-  </si>
-  <si>
-    <t>18562131-025</t>
-  </si>
-  <si>
-    <t>18562131-026</t>
-  </si>
-  <si>
-    <t>18562131-027</t>
-  </si>
-  <si>
-    <t>18562131-028</t>
-  </si>
-  <si>
-    <t>18562131-029</t>
-  </si>
-  <si>
-    <t>18562131-030</t>
-  </si>
-  <si>
-    <t>18562131-031</t>
-  </si>
-  <si>
-    <t>18562131-032</t>
-  </si>
-  <si>
-    <t>18562131-033</t>
-  </si>
-  <si>
-    <t>18562131-034</t>
-  </si>
-  <si>
-    <t>18562131-035</t>
-  </si>
-  <si>
-    <t>18562131-036</t>
-  </si>
-  <si>
-    <t>18562131-037</t>
-  </si>
-  <si>
-    <t>18562131-038</t>
-  </si>
-  <si>
-    <t>18562131-150</t>
-  </si>
-  <si>
-    <t>18562131-151</t>
-  </si>
-  <si>
-    <t>18562131-152</t>
-  </si>
-  <si>
-    <t>18562131-153</t>
-  </si>
-  <si>
-    <t>18562131-154</t>
-  </si>
-  <si>
-    <t>18562131-155</t>
-  </si>
-  <si>
-    <t>18562131-156</t>
-  </si>
-  <si>
-    <t>18566002-018</t>
-  </si>
-  <si>
-    <t>18566002-019</t>
-  </si>
-  <si>
-    <t>18566002-020</t>
-  </si>
-  <si>
-    <t>18566002-021</t>
-  </si>
-  <si>
-    <t>18566002-022</t>
-  </si>
-  <si>
-    <t>18566002-023</t>
-  </si>
-  <si>
-    <t>18566002-024</t>
-  </si>
-  <si>
-    <t>18566002-025</t>
-  </si>
-  <si>
-    <t>18566002-026</t>
-  </si>
-  <si>
-    <t>18566002-027</t>
-  </si>
-  <si>
-    <t>18566002-028</t>
-  </si>
-  <si>
-    <t>18566002-029</t>
-  </si>
-  <si>
-    <t>18566002-030</t>
-  </si>
-  <si>
-    <t>18566002-031</t>
-  </si>
-  <si>
-    <t>18566002-032</t>
-  </si>
-  <si>
-    <t>18566002-033</t>
-  </si>
-  <si>
-    <t>18566002-034</t>
-  </si>
-  <si>
-    <t>18566002-035</t>
-  </si>
-  <si>
-    <t>18566002-036</t>
-  </si>
-  <si>
-    <t>18566002-037</t>
-  </si>
-  <si>
-    <t>18566002-038</t>
-  </si>
-  <si>
-    <t>18566002-150</t>
-  </si>
-  <si>
-    <t>18566002-151</t>
-  </si>
-  <si>
-    <t>18566002-152</t>
-  </si>
-  <si>
-    <t>18566002-153</t>
-  </si>
-  <si>
-    <t>18566002-154</t>
-  </si>
-  <si>
-    <t>18566002-155</t>
-  </si>
-  <si>
-    <t>18566002-156</t>
-  </si>
-  <si>
-    <t>18669387-001</t>
-  </si>
-  <si>
-    <t>18687746-003</t>
-  </si>
-  <si>
-    <t>18750245-001</t>
-  </si>
-  <si>
-    <t>18750313-002</t>
-  </si>
-  <si>
-    <t>18750316-004</t>
-  </si>
-  <si>
-    <t>18758258-004</t>
-  </si>
-  <si>
-    <t>18786894-001</t>
-  </si>
-  <si>
-    <t>18867446-001</t>
-  </si>
-  <si>
-    <t>18916062-001</t>
-  </si>
-  <si>
-    <t>18930933-001</t>
-  </si>
-  <si>
-    <t>18937381-008</t>
-  </si>
-  <si>
-    <t>18957063-014</t>
-  </si>
-  <si>
-    <t>18965466-001</t>
-  </si>
-  <si>
-    <t>18979075-001</t>
-  </si>
-  <si>
-    <t>10698662-001</t>
-  </si>
-  <si>
-    <t>10797039-001</t>
-  </si>
-  <si>
-    <t>11352179-001</t>
-  </si>
-  <si>
-    <t>18449200-054</t>
-  </si>
-  <si>
-    <t>18654810-001</t>
-  </si>
-  <si>
-    <t>18654810-002</t>
-  </si>
-  <si>
-    <t>18654810-003</t>
-  </si>
-  <si>
-    <t>18654810-004</t>
-  </si>
-  <si>
-    <t>18654810-005</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="158">
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>16656274-219</t>
+  </si>
+  <si>
+    <t>16656274-220</t>
+  </si>
+  <si>
+    <t>16656274-221</t>
+  </si>
+  <si>
+    <t>16656274-222</t>
+  </si>
+  <si>
+    <t>16656274-223</t>
+  </si>
+  <si>
+    <t>16656274-224</t>
+  </si>
+  <si>
+    <t>16656274-225</t>
+  </si>
+  <si>
+    <t>16656274-226</t>
+  </si>
+  <si>
+    <t>16656274-227</t>
+  </si>
+  <si>
+    <t>16656274-228</t>
+  </si>
+  <si>
+    <t>16656274-229</t>
+  </si>
+  <si>
+    <t>16656274-230</t>
+  </si>
+  <si>
+    <t>16656274-231</t>
+  </si>
+  <si>
+    <t>16656274-232</t>
+  </si>
+  <si>
+    <t>16656274-233</t>
+  </si>
+  <si>
+    <t>16656274-234</t>
+  </si>
+  <si>
+    <t>16656274-235</t>
+  </si>
+  <si>
+    <t>16656274-236</t>
+  </si>
+  <si>
+    <t>16656274-237</t>
+  </si>
+  <si>
+    <t>16656274-238</t>
+  </si>
+  <si>
+    <t>16656274-239</t>
+  </si>
+  <si>
+    <t>16656274-240</t>
+  </si>
+  <si>
+    <t>16656274-241</t>
+  </si>
+  <si>
+    <t>16656274-242</t>
+  </si>
+  <si>
+    <t>16656274-243</t>
+  </si>
+  <si>
+    <t>16656274-244</t>
+  </si>
+  <si>
+    <t>16656274-245</t>
+  </si>
+  <si>
+    <t>16656274-246</t>
+  </si>
+  <si>
+    <t>16656274-247</t>
+  </si>
+  <si>
+    <t>16656274-248</t>
+  </si>
+  <si>
+    <t>16656274-249</t>
+  </si>
+  <si>
+    <t>16656274-250</t>
+  </si>
+  <si>
+    <t>16656274-251</t>
+  </si>
+  <si>
+    <t>16706273-229</t>
+  </si>
+  <si>
+    <t>16706273-230</t>
+  </si>
+  <si>
+    <t>16706273-231</t>
+  </si>
+  <si>
+    <t>16706273-232</t>
+  </si>
+  <si>
+    <t>16706273-233</t>
+  </si>
+  <si>
+    <t>16706273-234</t>
+  </si>
+  <si>
+    <t>16706273-235</t>
+  </si>
+  <si>
+    <t>16706273-236</t>
+  </si>
+  <si>
+    <t>16706273-237</t>
+  </si>
+  <si>
+    <t>16706273-238</t>
+  </si>
+  <si>
+    <t>16706273-239</t>
+  </si>
+  <si>
+    <t>16706273-240</t>
+  </si>
+  <si>
+    <t>16706273-241</t>
+  </si>
+  <si>
+    <t>16706273-242</t>
+  </si>
+  <si>
+    <t>16706273-243</t>
+  </si>
+  <si>
+    <t>16706273-244</t>
+  </si>
+  <si>
+    <t>16706273-245</t>
+  </si>
+  <si>
+    <t>16706273-246</t>
+  </si>
+  <si>
+    <t>16706273-247</t>
+  </si>
+  <si>
+    <t>16706273-248</t>
+  </si>
+  <si>
+    <t>16706273-249</t>
+  </si>
+  <si>
+    <t>16706273-250</t>
+  </si>
+  <si>
+    <t>16706273-251</t>
+  </si>
+  <si>
+    <t>16706273-252</t>
+  </si>
+  <si>
+    <t>16714743-021</t>
+  </si>
+  <si>
+    <t>16714743-022</t>
+  </si>
+  <si>
+    <t>16714743-023</t>
+  </si>
+  <si>
+    <t>17926860-023</t>
+  </si>
+  <si>
+    <t>17926860-024</t>
+  </si>
+  <si>
+    <t>17926860-025</t>
+  </si>
+  <si>
+    <t>17967270-029</t>
+  </si>
+  <si>
+    <t>17967270-030</t>
+  </si>
+  <si>
+    <t>17967270-031</t>
+  </si>
+  <si>
+    <t>17967270-032</t>
+  </si>
+  <si>
+    <t>17967270-033</t>
+  </si>
+  <si>
+    <t>17967270-034</t>
+  </si>
+  <si>
+    <t>18064695-007</t>
+  </si>
+  <si>
+    <t>18508384-001</t>
+  </si>
+  <si>
+    <t>18673023-086</t>
+  </si>
+  <si>
+    <t>19022675-001</t>
+  </si>
+  <si>
+    <t>19208804-001</t>
+  </si>
+  <si>
+    <t>19253737-001</t>
+  </si>
+  <si>
+    <t>19254133-001</t>
+  </si>
+  <si>
+    <t>19255690-001</t>
+  </si>
+  <si>
+    <t>19255690-002</t>
+  </si>
+  <si>
+    <t>19255690-003</t>
+  </si>
+  <si>
+    <t>19255690-004</t>
+  </si>
+  <si>
+    <t>19255690-005</t>
+  </si>
+  <si>
+    <t>19255690-006</t>
+  </si>
+  <si>
+    <t>19255690-007</t>
+  </si>
+  <si>
+    <t>19255690-008</t>
+  </si>
+  <si>
+    <t>19255690-009</t>
+  </si>
+  <si>
+    <t>19255690-010</t>
+  </si>
+  <si>
+    <t>19255690-011</t>
+  </si>
+  <si>
+    <t>19255690-012</t>
+  </si>
+  <si>
+    <t>19255690-013</t>
+  </si>
+  <si>
+    <t>19255690-014</t>
+  </si>
+  <si>
+    <t>19255690-015</t>
+  </si>
+  <si>
+    <t>19255690-016</t>
+  </si>
+  <si>
+    <t>19255690-017</t>
+  </si>
+  <si>
+    <t>19255690-018</t>
+  </si>
+  <si>
+    <t>19255690-019</t>
+  </si>
+  <si>
+    <t>19255690-020</t>
+  </si>
+  <si>
+    <t>19255690-021</t>
+  </si>
+  <si>
+    <t>19255690-022</t>
+  </si>
+  <si>
+    <t>19255690-023</t>
+  </si>
+  <si>
+    <t>19255690-024</t>
+  </si>
+  <si>
+    <t>19255690-025</t>
+  </si>
+  <si>
+    <t>19255690-026</t>
+  </si>
+  <si>
+    <t>19255690-027</t>
+  </si>
+  <si>
+    <t>19255690-028</t>
+  </si>
+  <si>
+    <t>19255690-029</t>
+  </si>
+  <si>
+    <t>19255690-030</t>
+  </si>
+  <si>
+    <t>19255690-031</t>
+  </si>
+  <si>
+    <t>19255690-032</t>
+  </si>
+  <si>
+    <t>19255690-033</t>
+  </si>
+  <si>
+    <t>19255690-034</t>
+  </si>
+  <si>
+    <t>19255690-035</t>
+  </si>
+  <si>
+    <t>19255690-036</t>
+  </si>
+  <si>
+    <t>19255690-037</t>
+  </si>
+  <si>
+    <t>19255690-038</t>
+  </si>
+  <si>
+    <t>19255690-039</t>
+  </si>
+  <si>
+    <t>19255690-040</t>
+  </si>
+  <si>
+    <t>19255690-041</t>
+  </si>
+  <si>
+    <t>19255690-042</t>
+  </si>
+  <si>
+    <t>19255690-043</t>
+  </si>
+  <si>
+    <t>19255690-044</t>
+  </si>
+  <si>
+    <t>19255690-045</t>
+  </si>
+  <si>
+    <t>19255690-046</t>
+  </si>
+  <si>
+    <t>19255690-047</t>
+  </si>
+  <si>
+    <t>19255690-048</t>
+  </si>
+  <si>
+    <t>19255690-049</t>
+  </si>
+  <si>
+    <t>19255690-050</t>
+  </si>
+  <si>
+    <t>19255690-051</t>
+  </si>
+  <si>
+    <t>19255690-052</t>
+  </si>
+  <si>
+    <t>19255690-053</t>
+  </si>
+  <si>
+    <t>19255690-054</t>
+  </si>
+  <si>
+    <t>19255690-055</t>
+  </si>
+  <si>
+    <t>19255690-056</t>
+  </si>
+  <si>
+    <t>19255690-057</t>
+  </si>
+  <si>
+    <t>19255690-058</t>
+  </si>
+  <si>
+    <t>19255690-059</t>
+  </si>
+  <si>
+    <t>19255690-060</t>
+  </si>
+  <si>
+    <t>19255690-061</t>
+  </si>
+  <si>
+    <t>19255690-062</t>
+  </si>
+  <si>
+    <t>19255690-063</t>
+  </si>
+  <si>
+    <t>19255690-064</t>
+  </si>
+  <si>
+    <t>19255690-065</t>
+  </si>
+  <si>
+    <t>19255690-066</t>
+  </si>
+  <si>
+    <t>19255690-067</t>
+  </si>
+  <si>
+    <t>19255690-068</t>
+  </si>
+  <si>
+    <t>19255690-069</t>
+  </si>
+  <si>
+    <t>19255690-070</t>
+  </si>
+  <si>
+    <t>19255690-071</t>
+  </si>
+  <si>
+    <t>19255690-072</t>
+  </si>
+  <si>
+    <t>19255690-073</t>
+  </si>
+  <si>
+    <t>19255690-076</t>
+  </si>
+  <si>
+    <t>19255690-077</t>
+  </si>
+  <si>
+    <t>19255690-078</t>
+  </si>
+  <si>
+    <t>19255690-079</t>
+  </si>
+  <si>
+    <t>19255690-080</t>
+  </si>
+  <si>
+    <t>19255690-081</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>0.06</t>
   </si>
 </sst>
 </file>
@@ -642,28 +516,28 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
     </font>
@@ -671,7 +545,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -679,7 +553,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -687,35 +561,35 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -723,7 +597,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -731,14 +605,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -746,14 +620,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -761,7 +635,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -769,21 +643,21 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -802,7 +676,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1150,7 +1024,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -1265,7 +1139,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1426,13 +1300,12 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="316" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="316" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="317">
     <cellStyle name="20% - Accent1" xfId="18" builtinId="30" customBuiltin="1"/>
@@ -1769,9 +1642,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1809,7 +1682,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1915,7 +1788,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2057,7 +1930,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2065,11 +1938,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{530DECDC-083C-432B-A02B-B8C551AF82A8}">
-  <dimension ref="A1:D199"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:D155"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.75" customWidth="1"/>
+    <col min="1" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="14" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2079,11 +1953,11 @@
       <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1">
-        <v>23.57</v>
-      </c>
-      <c r="D1">
-        <v>3.5000000000000003E-2</v>
+      <c r="C1">
+        <v>60.55</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2093,11 +1967,11 @@
       <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1">
-        <v>28.57</v>
-      </c>
-      <c r="D2">
-        <v>3.5000000000000003E-2</v>
+      <c r="C2">
+        <v>60.55</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2107,11 +1981,11 @@
       <c r="B3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="1">
-        <v>28.57</v>
-      </c>
-      <c r="D3">
-        <v>3.5000000000000003E-2</v>
+      <c r="C3">
+        <v>60.55</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2121,11 +1995,11 @@
       <c r="B4" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="1">
-        <v>18.57</v>
-      </c>
-      <c r="D4">
-        <v>3.5000000000000003E-2</v>
+      <c r="C4">
+        <v>71.34</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2135,11 +2009,11 @@
       <c r="B5" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="1">
-        <v>5.43</v>
-      </c>
-      <c r="D5">
-        <v>3.5000000000000003E-2</v>
+      <c r="C5">
+        <v>71.17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2149,11 +2023,11 @@
       <c r="B6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="D6">
-        <v>3.5000000000000003E-2</v>
+      <c r="C6">
+        <v>71.17</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2163,11 +2037,11 @@
       <c r="B7" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="1">
-        <v>0.95</v>
-      </c>
-      <c r="D7">
-        <v>3.5000000000000003E-2</v>
+      <c r="C7">
+        <v>71.150000000000006</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2177,11 +2051,11 @@
       <c r="B8" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="1">
-        <v>0.43</v>
-      </c>
-      <c r="D8">
-        <v>0.06</v>
+      <c r="C8">
+        <v>71.150000000000006</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2191,11 +2065,11 @@
       <c r="B9" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="1">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="D9">
-        <v>3.5000000000000003E-2</v>
+      <c r="C9">
+        <v>92.1</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2205,11 +2079,11 @@
       <c r="B10" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="1">
-        <v>2.64</v>
-      </c>
-      <c r="D10">
-        <v>3.5000000000000003E-2</v>
+      <c r="C10">
+        <v>92.1</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2219,11 +2093,11 @@
       <c r="B11" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="1">
-        <v>2.57</v>
-      </c>
-      <c r="D11">
-        <v>3.5000000000000003E-2</v>
+      <c r="C11">
+        <v>92.1</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2233,11 +2107,11 @@
       <c r="B12" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="1">
-        <v>1.41</v>
-      </c>
-      <c r="D12">
-        <v>3.5000000000000003E-2</v>
+      <c r="C12">
+        <v>92.1</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2247,11 +2121,11 @@
       <c r="B13" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="1">
-        <v>2.57</v>
-      </c>
-      <c r="D13">
-        <v>3.5000000000000003E-2</v>
+      <c r="C13">
+        <v>92.1</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2261,11 +2135,11 @@
       <c r="B14" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="1">
-        <v>7.43</v>
-      </c>
-      <c r="D14">
-        <v>3.5000000000000003E-2</v>
+      <c r="C14">
+        <v>92.1</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2275,11 +2149,11 @@
       <c r="B15" t="s">
         <v>0</v>
       </c>
-      <c r="C15" s="1">
-        <v>6.43</v>
-      </c>
-      <c r="D15">
-        <v>3.5000000000000003E-2</v>
+      <c r="C15">
+        <v>121.25</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2289,11 +2163,11 @@
       <c r="B16" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="1">
-        <v>6.43</v>
-      </c>
-      <c r="D16">
-        <v>3.5000000000000003E-2</v>
+      <c r="C16">
+        <v>121.25</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2303,11 +2177,11 @@
       <c r="B17" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="1">
-        <v>7.57</v>
-      </c>
-      <c r="D17">
-        <v>3.5000000000000003E-2</v>
+      <c r="C17">
+        <v>122.66</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2317,11 +2191,11 @@
       <c r="B18" t="s">
         <v>0</v>
       </c>
-      <c r="C18" s="1">
-        <v>7.57</v>
-      </c>
-      <c r="D18">
-        <v>0.06</v>
+      <c r="C18">
+        <v>122.66</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2331,11 +2205,11 @@
       <c r="B19" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="1">
-        <v>7.57</v>
-      </c>
-      <c r="D19">
-        <v>3.5000000000000003E-2</v>
+      <c r="C19">
+        <v>122.66</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2345,11 +2219,11 @@
       <c r="B20" t="s">
         <v>0</v>
       </c>
-      <c r="C20" s="1">
-        <v>7.57</v>
-      </c>
-      <c r="D20">
-        <v>3.5000000000000003E-2</v>
+      <c r="C20">
+        <v>122.66</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2359,11 +2233,11 @@
       <c r="B21" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="1">
-        <v>7.57</v>
-      </c>
-      <c r="D21">
-        <v>3.5000000000000003E-2</v>
+      <c r="C21">
+        <v>122.66</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2373,11 +2247,11 @@
       <c r="B22" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="1">
-        <v>7.57</v>
-      </c>
-      <c r="D22">
-        <v>3.5000000000000003E-2</v>
+      <c r="C22">
+        <v>152.74</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2387,11 +2261,11 @@
       <c r="B23" t="s">
         <v>0</v>
       </c>
-      <c r="C23" s="1">
-        <v>7.57</v>
-      </c>
-      <c r="D23">
-        <v>3.5000000000000003E-2</v>
+      <c r="C23">
+        <v>181.33</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2401,11 +2275,11 @@
       <c r="B24" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="1">
-        <v>7.57</v>
-      </c>
-      <c r="D24">
-        <v>3.5000000000000003E-2</v>
+      <c r="C24">
+        <v>181.33</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2415,11 +2289,11 @@
       <c r="B25" t="s">
         <v>0</v>
       </c>
-      <c r="C25" s="1">
-        <v>7.57</v>
-      </c>
-      <c r="D25">
-        <v>3.5000000000000003E-2</v>
+      <c r="C25">
+        <v>181.33</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2429,11 +2303,11 @@
       <c r="B26" t="s">
         <v>0</v>
       </c>
-      <c r="C26" s="1">
-        <v>6.43</v>
-      </c>
-      <c r="D26">
-        <v>3.5000000000000003E-2</v>
+      <c r="C26">
+        <v>207.88</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2443,11 +2317,11 @@
       <c r="B27" t="s">
         <v>0</v>
       </c>
-      <c r="C27" s="1">
-        <v>7.57</v>
-      </c>
-      <c r="D27">
-        <v>3.5000000000000003E-2</v>
+      <c r="C27">
+        <v>257.47000000000003</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2457,11 +2331,11 @@
       <c r="B28" t="s">
         <v>0</v>
       </c>
-      <c r="C28" s="1">
-        <v>12.57</v>
-      </c>
-      <c r="D28">
-        <v>3.5000000000000003E-2</v>
+      <c r="C28">
+        <v>326.73</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2471,11 +2345,11 @@
       <c r="B29" t="s">
         <v>0</v>
       </c>
-      <c r="C29" s="1">
-        <v>16.43</v>
-      </c>
-      <c r="D29">
-        <v>3.5000000000000003E-2</v>
+      <c r="C29">
+        <v>326.73</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2485,11 +2359,11 @@
       <c r="B30" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="1">
-        <v>52.57</v>
-      </c>
-      <c r="D30">
-        <v>3.5000000000000003E-2</v>
+      <c r="C30">
+        <v>326.73</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2499,11 +2373,11 @@
       <c r="B31" t="s">
         <v>0</v>
       </c>
-      <c r="C31" s="1">
-        <v>53.57</v>
-      </c>
-      <c r="D31">
-        <v>3.5000000000000003E-2</v>
+      <c r="C31">
+        <v>389.98</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2513,11 +2387,11 @@
       <c r="B32" t="s">
         <v>0</v>
       </c>
-      <c r="C32" s="1">
-        <v>54.43</v>
-      </c>
-      <c r="D32">
-        <v>3.5000000000000003E-2</v>
+      <c r="C32">
+        <v>530.54999999999995</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2527,11 +2401,11 @@
       <c r="B33" t="s">
         <v>0</v>
       </c>
-      <c r="C33" s="1">
-        <v>119.57</v>
-      </c>
-      <c r="D33">
-        <v>3.5000000000000003E-2</v>
+      <c r="C33">
+        <v>661.62</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2541,11 +2415,11 @@
       <c r="B34" t="s">
         <v>0</v>
       </c>
-      <c r="C34" s="1">
-        <v>38.57</v>
-      </c>
-      <c r="D34">
-        <v>3.5000000000000003E-2</v>
+      <c r="C34">
+        <v>30.03</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2555,11 +2429,11 @@
       <c r="B35" t="s">
         <v>0</v>
       </c>
-      <c r="C35" s="1">
-        <v>69.430000000000007</v>
-      </c>
-      <c r="D35">
-        <v>3.5000000000000003E-2</v>
+      <c r="C35">
+        <v>30.03</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2569,11 +2443,11 @@
       <c r="B36" t="s">
         <v>0</v>
       </c>
-      <c r="C36" s="1">
-        <v>38.57</v>
-      </c>
-      <c r="D36">
-        <v>3.5000000000000003E-2</v>
+      <c r="C36">
+        <v>30.03</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2583,11 +2457,11 @@
       <c r="B37" t="s">
         <v>0</v>
       </c>
-      <c r="C37" s="1">
-        <v>63.43</v>
-      </c>
-      <c r="D37">
-        <v>0.06</v>
+      <c r="C37">
+        <v>30.03</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2597,11 +2471,11 @@
       <c r="B38" t="s">
         <v>0</v>
       </c>
-      <c r="C38" s="1">
-        <v>60.43</v>
-      </c>
-      <c r="D38">
-        <v>3.5000000000000003E-2</v>
+      <c r="C38">
+        <v>30.03</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2611,11 +2485,11 @@
       <c r="B39" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="1">
-        <v>93.43</v>
-      </c>
-      <c r="D39">
-        <v>3.5000000000000003E-2</v>
+      <c r="C39">
+        <v>30.03</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2625,11 +2499,11 @@
       <c r="B40" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="1">
-        <v>93.43</v>
-      </c>
-      <c r="D40">
-        <v>3.5000000000000003E-2</v>
+      <c r="C40">
+        <v>30.03</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2639,11 +2513,11 @@
       <c r="B41" t="s">
         <v>0</v>
       </c>
-      <c r="C41" s="1">
-        <v>93.43</v>
-      </c>
-      <c r="D41">
-        <v>3.5000000000000003E-2</v>
+      <c r="C41">
+        <v>30.03</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2653,11 +2527,11 @@
       <c r="B42" t="s">
         <v>0</v>
       </c>
-      <c r="C42" s="1">
-        <v>92.43</v>
-      </c>
-      <c r="D42">
-        <v>3.5000000000000003E-2</v>
+      <c r="C42">
+        <v>30.03</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2667,11 +2541,11 @@
       <c r="B43" t="s">
         <v>0</v>
       </c>
-      <c r="C43" s="1">
-        <v>92.43</v>
-      </c>
-      <c r="D43">
-        <v>3.5000000000000003E-2</v>
+      <c r="C43">
+        <v>30.03</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2681,11 +2555,11 @@
       <c r="B44" t="s">
         <v>0</v>
       </c>
-      <c r="C44" s="1">
-        <v>54.43</v>
-      </c>
-      <c r="D44">
-        <v>3.5000000000000003E-2</v>
+      <c r="C44">
+        <v>30.03</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2695,11 +2569,11 @@
       <c r="B45" t="s">
         <v>0</v>
       </c>
-      <c r="C45" s="1">
-        <v>96.57</v>
-      </c>
-      <c r="D45">
-        <v>3.5000000000000003E-2</v>
+      <c r="C45">
+        <v>17.920000000000002</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2709,11 +2583,11 @@
       <c r="B46" t="s">
         <v>0</v>
       </c>
-      <c r="C46" s="1">
-        <v>54.43</v>
-      </c>
-      <c r="D46">
-        <v>3.5000000000000003E-2</v>
+      <c r="C46">
+        <v>17.920000000000002</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2723,11 +2597,11 @@
       <c r="B47" t="s">
         <v>0</v>
       </c>
-      <c r="C47" s="1">
-        <v>54.43</v>
-      </c>
-      <c r="D47">
-        <v>3.5000000000000003E-2</v>
+      <c r="C47">
+        <v>17.920000000000002</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2737,11 +2611,11 @@
       <c r="B48" t="s">
         <v>0</v>
       </c>
-      <c r="C48" s="1">
-        <v>19.43</v>
-      </c>
-      <c r="D48">
-        <v>3.5000000000000003E-2</v>
+      <c r="C48">
+        <v>17.920000000000002</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2751,11 +2625,11 @@
       <c r="B49" t="s">
         <v>0</v>
       </c>
-      <c r="C49" s="1">
-        <v>103.43</v>
-      </c>
-      <c r="D49">
-        <v>3.5000000000000003E-2</v>
+      <c r="C49">
+        <v>17.920000000000002</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2765,11 +2639,11 @@
       <c r="B50" t="s">
         <v>0</v>
       </c>
-      <c r="C50" s="1">
-        <v>103.43</v>
-      </c>
-      <c r="D50">
-        <v>3.5000000000000003E-2</v>
+      <c r="C50">
+        <v>17.920000000000002</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2779,11 +2653,11 @@
       <c r="B51" t="s">
         <v>0</v>
       </c>
-      <c r="C51" s="1">
-        <v>33.57</v>
-      </c>
-      <c r="D51">
-        <v>3.5000000000000003E-2</v>
+      <c r="C51">
+        <v>17.920000000000002</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2793,11 +2667,11 @@
       <c r="B52" t="s">
         <v>0</v>
       </c>
-      <c r="C52" s="1">
-        <v>46.43</v>
-      </c>
-      <c r="D52">
-        <v>3.5000000000000003E-2</v>
+      <c r="C52">
+        <v>17.920000000000002</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2807,11 +2681,11 @@
       <c r="B53" t="s">
         <v>0</v>
       </c>
-      <c r="C53" s="1">
-        <v>52.57</v>
-      </c>
-      <c r="D53">
-        <v>3.5000000000000003E-2</v>
+      <c r="C53">
+        <v>17.920000000000002</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2821,11 +2695,11 @@
       <c r="B54" t="s">
         <v>0</v>
       </c>
-      <c r="C54" s="1">
-        <v>165.57</v>
-      </c>
-      <c r="D54">
-        <v>3.5000000000000003E-2</v>
+      <c r="C54">
+        <v>17.920000000000002</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2835,11 +2709,11 @@
       <c r="B55" t="s">
         <v>0</v>
       </c>
-      <c r="C55" s="1">
-        <v>213.57</v>
-      </c>
-      <c r="D55">
-        <v>3.5000000000000003E-2</v>
+      <c r="C55">
+        <v>17.920000000000002</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2849,11 +2723,11 @@
       <c r="B56" t="s">
         <v>0</v>
       </c>
-      <c r="C56" s="1">
-        <v>213.57</v>
-      </c>
-      <c r="D56">
-        <v>3.5000000000000003E-2</v>
+      <c r="C56">
+        <v>17.920000000000002</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2863,11 +2737,11 @@
       <c r="B57" t="s">
         <v>0</v>
       </c>
-      <c r="C57" s="1">
-        <v>132.43</v>
-      </c>
-      <c r="D57">
-        <v>3.5000000000000003E-2</v>
+      <c r="C57">
+        <v>17.920000000000002</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2877,11 +2751,11 @@
       <c r="B58" t="s">
         <v>0</v>
       </c>
-      <c r="C58" s="1">
-        <v>134.43</v>
-      </c>
-      <c r="D58">
-        <v>3.5000000000000003E-2</v>
+      <c r="C58">
+        <v>62.63</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2891,11 +2765,11 @@
       <c r="B59" t="s">
         <v>0</v>
       </c>
-      <c r="C59" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D59">
-        <v>3.5000000000000003E-2</v>
+      <c r="C59">
+        <v>108.63</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2905,11 +2779,11 @@
       <c r="B60" t="s">
         <v>0</v>
       </c>
-      <c r="C60" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D60">
-        <v>3.5000000000000003E-2</v>
+      <c r="C60">
+        <v>108.63</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2919,11 +2793,11 @@
       <c r="B61" t="s">
         <v>0</v>
       </c>
-      <c r="C61" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D61">
-        <v>3.5000000000000003E-2</v>
+      <c r="C61">
+        <v>3066.17</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2933,11 +2807,11 @@
       <c r="B62" t="s">
         <v>0</v>
       </c>
-      <c r="C62" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D62">
-        <v>3.5000000000000003E-2</v>
+      <c r="C62">
+        <v>1309.05</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2947,11 +2821,11 @@
       <c r="B63" t="s">
         <v>0</v>
       </c>
-      <c r="C63" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D63">
-        <v>3.5000000000000003E-2</v>
+      <c r="C63">
+        <v>899.73</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2961,11 +2835,11 @@
       <c r="B64" t="s">
         <v>0</v>
       </c>
-      <c r="C64" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D64">
-        <v>3.5000000000000003E-2</v>
+      <c r="C64">
+        <v>67.489999999999995</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2975,11 +2849,11 @@
       <c r="B65" t="s">
         <v>0</v>
       </c>
-      <c r="C65" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D65">
-        <v>3.5000000000000003E-2</v>
+      <c r="C65">
+        <v>67.489999999999995</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2989,11 +2863,11 @@
       <c r="B66" t="s">
         <v>0</v>
       </c>
-      <c r="C66" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D66">
-        <v>3.5000000000000003E-2</v>
+      <c r="C66">
+        <v>67.55</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3003,11 +2877,11 @@
       <c r="B67" t="s">
         <v>0</v>
       </c>
-      <c r="C67" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D67">
-        <v>3.5000000000000003E-2</v>
+      <c r="C67">
+        <v>52.94</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3017,11 +2891,11 @@
       <c r="B68" t="s">
         <v>0</v>
       </c>
-      <c r="C68" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D68">
-        <v>3.5000000000000003E-2</v>
+      <c r="C68">
+        <v>52.94</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3031,11 +2905,11 @@
       <c r="B69" t="s">
         <v>0</v>
       </c>
-      <c r="C69" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D69">
-        <v>3.5000000000000003E-2</v>
+      <c r="C69">
+        <v>52.92</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3045,11 +2919,11 @@
       <c r="B70" t="s">
         <v>0</v>
       </c>
-      <c r="C70" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D70">
-        <v>3.5000000000000003E-2</v>
+      <c r="C70">
+        <v>310.27</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3059,11 +2933,11 @@
       <c r="B71" t="s">
         <v>0</v>
       </c>
-      <c r="C71" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D71">
-        <v>3.5000000000000003E-2</v>
+      <c r="C71">
+        <v>304.61</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3073,11 +2947,11 @@
       <c r="B72" t="s">
         <v>0</v>
       </c>
-      <c r="C72" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D72">
-        <v>3.5000000000000003E-2</v>
+      <c r="C72">
+        <v>81.39</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3087,11 +2961,11 @@
       <c r="B73" t="s">
         <v>0</v>
       </c>
-      <c r="C73" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D73">
-        <v>3.5000000000000003E-2</v>
+      <c r="C73">
+        <v>3036.04</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3101,11 +2975,11 @@
       <c r="B74" t="s">
         <v>0</v>
       </c>
-      <c r="C74" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D74">
-        <v>3.5000000000000003E-2</v>
+      <c r="C74">
+        <v>30476.16</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3115,11 +2989,11 @@
       <c r="B75" t="s">
         <v>0</v>
       </c>
-      <c r="C75" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D75">
-        <v>3.5000000000000003E-2</v>
+      <c r="C75">
+        <v>14.36</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3129,11 +3003,11 @@
       <c r="B76" t="s">
         <v>0</v>
       </c>
-      <c r="C76" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D76">
-        <v>3.5000000000000003E-2</v>
+      <c r="C76">
+        <v>249.35</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3143,11 +3017,11 @@
       <c r="B77" t="s">
         <v>0</v>
       </c>
-      <c r="C77" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D77">
-        <v>3.5000000000000003E-2</v>
+      <c r="C77">
+        <v>15.02</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3157,11 +3031,11 @@
       <c r="B78" t="s">
         <v>0</v>
       </c>
-      <c r="C78" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D78">
-        <v>3.5000000000000003E-2</v>
+      <c r="C78">
+        <v>15.02</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3171,11 +3045,11 @@
       <c r="B79" t="s">
         <v>0</v>
       </c>
-      <c r="C79" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D79">
-        <v>3.5000000000000003E-2</v>
+      <c r="C79">
+        <v>15.02</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3185,11 +3059,11 @@
       <c r="B80" t="s">
         <v>0</v>
       </c>
-      <c r="C80" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D80">
-        <v>3.5000000000000003E-2</v>
+      <c r="C80">
+        <v>15.02</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3199,11 +3073,11 @@
       <c r="B81" t="s">
         <v>0</v>
       </c>
-      <c r="C81" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D81">
-        <v>3.5000000000000003E-2</v>
+      <c r="C81">
+        <v>15.02</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3213,11 +3087,11 @@
       <c r="B82" t="s">
         <v>0</v>
       </c>
-      <c r="C82" s="1">
-        <v>130.43</v>
-      </c>
-      <c r="D82">
-        <v>3.5000000000000003E-2</v>
+      <c r="C82">
+        <v>15.02</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3227,11 +3101,11 @@
       <c r="B83" t="s">
         <v>0</v>
       </c>
-      <c r="C83" s="1">
-        <v>707.57</v>
-      </c>
-      <c r="D83">
-        <v>3.5000000000000003E-2</v>
+      <c r="C83">
+        <v>26.16</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3241,11 +3115,11 @@
       <c r="B84" t="s">
         <v>0</v>
       </c>
-      <c r="C84" s="1">
-        <v>585.42999999999995</v>
-      </c>
-      <c r="D84">
-        <v>3.5000000000000003E-2</v>
+      <c r="C84">
+        <v>26.16</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3255,11 +3129,11 @@
       <c r="B85" t="s">
         <v>0</v>
       </c>
-      <c r="C85" s="1">
-        <v>293.43</v>
-      </c>
-      <c r="D85">
-        <v>3.5000000000000003E-2</v>
+      <c r="C85">
+        <v>26.16</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3269,11 +3143,11 @@
       <c r="B86" t="s">
         <v>0</v>
       </c>
-      <c r="C86" s="1">
-        <v>732.57</v>
-      </c>
-      <c r="D86">
-        <v>3.5000000000000003E-2</v>
+      <c r="C86">
+        <v>26.16</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3283,11 +3157,11 @@
       <c r="B87" t="s">
         <v>0</v>
       </c>
-      <c r="C87" s="1">
-        <v>368.43</v>
-      </c>
-      <c r="D87">
-        <v>3.5000000000000003E-2</v>
+      <c r="C87">
+        <v>26.16</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3297,11 +3171,11 @@
       <c r="B88" t="s">
         <v>0</v>
       </c>
-      <c r="C88" s="1">
-        <v>567.42999999999995</v>
-      </c>
-      <c r="D88">
-        <v>3.5000000000000003E-2</v>
+      <c r="C88">
+        <v>26.16</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3311,11 +3185,11 @@
       <c r="B89" t="s">
         <v>0</v>
       </c>
-      <c r="C89" s="1">
-        <v>1343.43</v>
-      </c>
-      <c r="D89">
-        <v>3.5000000000000003E-2</v>
+      <c r="C89">
+        <v>26.16</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3325,11 +3199,11 @@
       <c r="B90" t="s">
         <v>0</v>
       </c>
-      <c r="C90" s="1">
-        <v>567.42999999999995</v>
-      </c>
-      <c r="D90">
-        <v>3.5000000000000003E-2</v>
+      <c r="C90">
+        <v>26.16</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3339,11 +3213,11 @@
       <c r="B91" t="s">
         <v>0</v>
       </c>
-      <c r="C91" s="1">
-        <v>497.43</v>
-      </c>
-      <c r="D91">
-        <v>3.5000000000000003E-2</v>
+      <c r="C91">
+        <v>26.16</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3353,11 +3227,11 @@
       <c r="B92" t="s">
         <v>0</v>
       </c>
-      <c r="C92" s="1">
-        <v>699.57</v>
-      </c>
-      <c r="D92">
-        <v>3.5000000000000003E-2</v>
+      <c r="C92">
+        <v>26.16</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3367,11 +3241,11 @@
       <c r="B93" t="s">
         <v>0</v>
       </c>
-      <c r="C93" s="1">
-        <v>957.57</v>
-      </c>
-      <c r="D93">
-        <v>0.06</v>
+      <c r="C93">
+        <v>26.16</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3381,11 +3255,11 @@
       <c r="B94" t="s">
         <v>0</v>
       </c>
-      <c r="C94" s="1">
-        <v>22785.57</v>
-      </c>
-      <c r="D94">
-        <v>0.06</v>
+      <c r="C94">
+        <v>26.16</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3395,11 +3269,11 @@
       <c r="B95" t="s">
         <v>0</v>
       </c>
-      <c r="C95" s="1">
-        <v>6523.43</v>
-      </c>
-      <c r="D95">
-        <v>3.5000000000000003E-2</v>
+      <c r="C95">
+        <v>26.16</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3409,11 +3283,11 @@
       <c r="B96" t="s">
         <v>0</v>
       </c>
-      <c r="C96" s="1">
-        <v>22112.43</v>
-      </c>
-      <c r="D96">
-        <v>3.5000000000000003E-2</v>
+      <c r="C96">
+        <v>26.16</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3423,11 +3297,11 @@
       <c r="B97" t="s">
         <v>0</v>
       </c>
-      <c r="C97" s="1">
-        <v>143.03</v>
-      </c>
-      <c r="D97">
-        <v>3.5000000000000003E-2</v>
+      <c r="C97">
+        <v>26.16</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3437,11 +3311,11 @@
       <c r="B98" t="s">
         <v>0</v>
       </c>
-      <c r="C98" s="1">
-        <v>46401.24</v>
-      </c>
-      <c r="D98">
-        <v>3.5000000000000003E-2</v>
+      <c r="C98">
+        <v>26.16</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3451,11 +3325,11 @@
       <c r="B99" t="s">
         <v>0</v>
       </c>
-      <c r="C99" s="1">
-        <v>20815.759999999998</v>
-      </c>
-      <c r="D99">
-        <v>3.5000000000000003E-2</v>
+      <c r="C99">
+        <v>26.16</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3465,11 +3339,11 @@
       <c r="B100" t="s">
         <v>0</v>
       </c>
-      <c r="C100" s="1">
-        <v>20815.759999999998</v>
-      </c>
-      <c r="D100">
-        <v>3.5000000000000003E-2</v>
+      <c r="C100">
+        <v>26.16</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3479,11 +3353,11 @@
       <c r="B101" t="s">
         <v>0</v>
       </c>
-      <c r="C101" s="1">
-        <v>25303.759999999998</v>
-      </c>
-      <c r="D101">
-        <v>0.06</v>
+      <c r="C101">
+        <v>26.16</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3493,11 +3367,11 @@
       <c r="B102" t="s">
         <v>0</v>
       </c>
-      <c r="C102" s="1">
-        <v>60862.76</v>
-      </c>
-      <c r="D102">
-        <v>0.06</v>
+      <c r="C102">
+        <v>26.16</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3507,11 +3381,11 @@
       <c r="B103" t="s">
         <v>0</v>
       </c>
-      <c r="C103" s="1">
-        <v>707.24</v>
-      </c>
-      <c r="D103">
-        <v>3.5000000000000003E-2</v>
+      <c r="C103">
+        <v>26.16</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3521,11 +3395,11 @@
       <c r="B104" t="s">
         <v>0</v>
       </c>
-      <c r="C104" s="1">
-        <v>707.24</v>
-      </c>
-      <c r="D104">
-        <v>3.5000000000000003E-2</v>
+      <c r="C104">
+        <v>26.16</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3535,11 +3409,11 @@
       <c r="B105" t="s">
         <v>0</v>
       </c>
-      <c r="C105" s="1">
-        <v>786.24</v>
-      </c>
-      <c r="D105">
-        <v>3.5000000000000003E-2</v>
+      <c r="C105">
+        <v>26.16</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3549,11 +3423,11 @@
       <c r="B106" t="s">
         <v>0</v>
       </c>
-      <c r="C106" s="1">
-        <v>472.24</v>
-      </c>
-      <c r="D106">
-        <v>3.5000000000000003E-2</v>
+      <c r="C106">
+        <v>26.16</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3563,11 +3437,11 @@
       <c r="B107" t="s">
         <v>0</v>
       </c>
-      <c r="C107" s="1">
-        <v>472.24</v>
-      </c>
-      <c r="D107">
-        <v>3.5000000000000003E-2</v>
+      <c r="C107">
+        <v>26.16</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3577,11 +3451,11 @@
       <c r="B108" t="s">
         <v>0</v>
       </c>
-      <c r="C108" s="1">
-        <v>472.24</v>
-      </c>
-      <c r="D108">
-        <v>3.5000000000000003E-2</v>
+      <c r="C108">
+        <v>26.16</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3591,11 +3465,11 @@
       <c r="B109" t="s">
         <v>0</v>
       </c>
-      <c r="C109" s="1">
-        <v>472.24</v>
-      </c>
-      <c r="D109">
-        <v>3.5000000000000003E-2</v>
+      <c r="C109">
+        <v>26.16</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3605,11 +3479,11 @@
       <c r="B110" t="s">
         <v>0</v>
       </c>
-      <c r="C110" s="1">
-        <v>472.24</v>
-      </c>
-      <c r="D110">
-        <v>3.5000000000000003E-2</v>
+      <c r="C110">
+        <v>26.16</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3619,11 +3493,11 @@
       <c r="B111" t="s">
         <v>0</v>
       </c>
-      <c r="C111" s="1">
-        <v>472.24</v>
-      </c>
-      <c r="D111">
-        <v>3.5000000000000003E-2</v>
+      <c r="C111">
+        <v>26.16</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3633,11 +3507,11 @@
       <c r="B112" t="s">
         <v>0</v>
       </c>
-      <c r="C112" s="1">
-        <v>472.24</v>
-      </c>
-      <c r="D112">
-        <v>3.5000000000000003E-2</v>
+      <c r="C112">
+        <v>26.16</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3647,11 +3521,11 @@
       <c r="B113" t="s">
         <v>0</v>
       </c>
-      <c r="C113" s="1">
-        <v>472.24</v>
-      </c>
-      <c r="D113">
-        <v>3.5000000000000003E-2</v>
+      <c r="C113">
+        <v>26.16</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3661,11 +3535,11 @@
       <c r="B114" t="s">
         <v>0</v>
       </c>
-      <c r="C114" s="1">
-        <v>364.76</v>
-      </c>
-      <c r="D114">
-        <v>3.5000000000000003E-2</v>
+      <c r="C114">
+        <v>26.16</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3675,11 +3549,11 @@
       <c r="B115" t="s">
         <v>0</v>
       </c>
-      <c r="C115" s="1">
-        <v>337.76</v>
-      </c>
-      <c r="D115">
-        <v>3.5000000000000003E-2</v>
+      <c r="C115">
+        <v>26.16</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3689,11 +3563,11 @@
       <c r="B116" t="s">
         <v>0</v>
       </c>
-      <c r="C116" s="1">
-        <v>254.76</v>
-      </c>
-      <c r="D116">
-        <v>3.5000000000000003E-2</v>
+      <c r="C116">
+        <v>26.16</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3703,11 +3577,11 @@
       <c r="B117" t="s">
         <v>0</v>
       </c>
-      <c r="C117" s="1">
-        <v>90.24</v>
-      </c>
-      <c r="D117">
-        <v>0.06</v>
+      <c r="C117">
+        <v>26.16</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3717,11 +3591,11 @@
       <c r="B118" t="s">
         <v>0</v>
       </c>
-      <c r="C118" s="1">
-        <v>125.24</v>
-      </c>
-      <c r="D118">
-        <v>3.5000000000000003E-2</v>
+      <c r="C118">
+        <v>26.16</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3731,11 +3605,11 @@
       <c r="B119" t="s">
         <v>0</v>
       </c>
-      <c r="C119" s="1">
-        <v>211.24</v>
-      </c>
-      <c r="D119">
-        <v>3.5000000000000003E-2</v>
+      <c r="C119">
+        <v>26.16</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3745,11 +3619,11 @@
       <c r="B120" t="s">
         <v>0</v>
       </c>
-      <c r="C120" s="1">
-        <v>180.24</v>
-      </c>
-      <c r="D120">
-        <v>3.5000000000000003E-2</v>
+      <c r="C120">
+        <v>26.16</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3759,11 +3633,11 @@
       <c r="B121" t="s">
         <v>0</v>
       </c>
-      <c r="C121" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D121">
-        <v>3.5000000000000003E-2</v>
+      <c r="C121">
+        <v>26.16</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3773,11 +3647,11 @@
       <c r="B122" t="s">
         <v>0</v>
       </c>
-      <c r="C122" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D122">
-        <v>3.5000000000000003E-2</v>
+      <c r="C122">
+        <v>26.16</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3787,11 +3661,11 @@
       <c r="B123" t="s">
         <v>0</v>
       </c>
-      <c r="C123" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D123">
-        <v>3.5000000000000003E-2</v>
+      <c r="C123">
+        <v>26.16</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3801,11 +3675,11 @@
       <c r="B124" t="s">
         <v>0</v>
       </c>
-      <c r="C124" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D124">
-        <v>3.5000000000000003E-2</v>
+      <c r="C124">
+        <v>26.16</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3815,11 +3689,11 @@
       <c r="B125" t="s">
         <v>0</v>
       </c>
-      <c r="C125" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D125">
-        <v>3.5000000000000003E-2</v>
+      <c r="C125">
+        <v>26.16</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3829,11 +3703,11 @@
       <c r="B126" t="s">
         <v>0</v>
       </c>
-      <c r="C126" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D126">
-        <v>3.5000000000000003E-2</v>
+      <c r="C126">
+        <v>26.16</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3843,11 +3717,11 @@
       <c r="B127" t="s">
         <v>0</v>
       </c>
-      <c r="C127" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D127">
-        <v>3.5000000000000003E-2</v>
+      <c r="C127">
+        <v>26.16</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3857,11 +3731,11 @@
       <c r="B128" t="s">
         <v>0</v>
       </c>
-      <c r="C128" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D128">
-        <v>3.5000000000000003E-2</v>
+      <c r="C128">
+        <v>26.16</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3871,11 +3745,11 @@
       <c r="B129" t="s">
         <v>0</v>
       </c>
-      <c r="C129" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D129">
-        <v>3.5000000000000003E-2</v>
+      <c r="C129">
+        <v>26.16</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3885,11 +3759,11 @@
       <c r="B130" t="s">
         <v>0</v>
       </c>
-      <c r="C130" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D130">
-        <v>3.5000000000000003E-2</v>
+      <c r="C130">
+        <v>26.16</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3899,11 +3773,11 @@
       <c r="B131" t="s">
         <v>0</v>
       </c>
-      <c r="C131" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D131">
-        <v>3.5000000000000003E-2</v>
+      <c r="C131">
+        <v>26.16</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3913,11 +3787,11 @@
       <c r="B132" t="s">
         <v>0</v>
       </c>
-      <c r="C132" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D132">
-        <v>3.5000000000000003E-2</v>
+      <c r="C132">
+        <v>26.16</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3927,11 +3801,11 @@
       <c r="B133" t="s">
         <v>0</v>
       </c>
-      <c r="C133" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D133">
-        <v>3.5000000000000003E-2</v>
+      <c r="C133">
+        <v>26.16</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3941,11 +3815,11 @@
       <c r="B134" t="s">
         <v>0</v>
       </c>
-      <c r="C134" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D134">
-        <v>3.5000000000000003E-2</v>
+      <c r="C134">
+        <v>26.16</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3955,11 +3829,11 @@
       <c r="B135" t="s">
         <v>0</v>
       </c>
-      <c r="C135" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D135">
-        <v>3.5000000000000003E-2</v>
+      <c r="C135">
+        <v>26.16</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3969,11 +3843,11 @@
       <c r="B136" t="s">
         <v>0</v>
       </c>
-      <c r="C136" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D136">
-        <v>3.5000000000000003E-2</v>
+      <c r="C136">
+        <v>26.16</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3983,11 +3857,11 @@
       <c r="B137" t="s">
         <v>0</v>
       </c>
-      <c r="C137" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D137">
-        <v>3.5000000000000003E-2</v>
+      <c r="C137">
+        <v>26.16</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3997,11 +3871,11 @@
       <c r="B138" t="s">
         <v>0</v>
       </c>
-      <c r="C138" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D138">
-        <v>3.5000000000000003E-2</v>
+      <c r="C138">
+        <v>26.16</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4011,11 +3885,11 @@
       <c r="B139" t="s">
         <v>0</v>
       </c>
-      <c r="C139" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D139">
-        <v>3.5000000000000003E-2</v>
+      <c r="C139">
+        <v>26.16</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4025,11 +3899,11 @@
       <c r="B140" t="s">
         <v>0</v>
       </c>
-      <c r="C140" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D140">
-        <v>3.5000000000000003E-2</v>
+      <c r="C140">
+        <v>26.16</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4039,11 +3913,11 @@
       <c r="B141" t="s">
         <v>0</v>
       </c>
-      <c r="C141" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D141">
-        <v>3.5000000000000003E-2</v>
+      <c r="C141">
+        <v>26.16</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4053,11 +3927,11 @@
       <c r="B142" t="s">
         <v>0</v>
       </c>
-      <c r="C142" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D142">
-        <v>3.5000000000000003E-2</v>
+      <c r="C142">
+        <v>26.16</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4067,11 +3941,11 @@
       <c r="B143" t="s">
         <v>0</v>
       </c>
-      <c r="C143" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D143">
-        <v>3.5000000000000003E-2</v>
+      <c r="C143">
+        <v>14.05</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4081,11 +3955,11 @@
       <c r="B144" t="s">
         <v>0</v>
       </c>
-      <c r="C144" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D144">
-        <v>3.5000000000000003E-2</v>
+      <c r="C144">
+        <v>27.62</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4095,11 +3969,11 @@
       <c r="B145" t="s">
         <v>0</v>
       </c>
-      <c r="C145" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D145">
-        <v>3.5000000000000003E-2</v>
+      <c r="C145">
+        <v>39.72</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4109,11 +3983,11 @@
       <c r="B146" t="s">
         <v>0</v>
       </c>
-      <c r="C146" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D146">
-        <v>3.5000000000000003E-2</v>
+      <c r="C146">
+        <v>39.72</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4123,11 +3997,11 @@
       <c r="B147" t="s">
         <v>0</v>
       </c>
-      <c r="C147" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D147">
-        <v>3.5000000000000003E-2</v>
+      <c r="C147">
+        <v>39.72</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4137,11 +4011,11 @@
       <c r="B148" t="s">
         <v>0</v>
       </c>
-      <c r="C148" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D148">
-        <v>3.5000000000000003E-2</v>
+      <c r="C148">
+        <v>39.72</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4151,11 +4025,11 @@
       <c r="B149" t="s">
         <v>0</v>
       </c>
-      <c r="C149" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D149">
-        <v>3.5000000000000003E-2</v>
+      <c r="C149">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4165,11 +4039,11 @@
       <c r="B150" t="s">
         <v>0</v>
       </c>
-      <c r="C150" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D150">
-        <v>3.5000000000000003E-2</v>
+      <c r="C150">
+        <v>35.25</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4179,11 +4053,11 @@
       <c r="B151" t="s">
         <v>0</v>
       </c>
-      <c r="C151" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D151">
-        <v>3.5000000000000003E-2</v>
+      <c r="C151">
+        <v>58.11</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4193,11 +4067,11 @@
       <c r="B152" t="s">
         <v>0</v>
       </c>
-      <c r="C152" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D152">
-        <v>3.5000000000000003E-2</v>
+      <c r="C152">
+        <v>99.07</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4207,11 +4081,11 @@
       <c r="B153" t="s">
         <v>0</v>
       </c>
-      <c r="C153" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D153">
-        <v>3.5000000000000003E-2</v>
+      <c r="C153">
+        <v>99.07</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4221,11 +4095,11 @@
       <c r="B154" t="s">
         <v>0</v>
       </c>
-      <c r="C154" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D154">
-        <v>3.5000000000000003E-2</v>
+      <c r="C154">
+        <v>99.07</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4235,627 +4109,11 @@
       <c r="B155" t="s">
         <v>0</v>
       </c>
-      <c r="C155" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D155">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4">
-      <c r="A156" t="s">
-        <v>156</v>
-      </c>
-      <c r="B156" t="s">
-        <v>0</v>
-      </c>
-      <c r="C156" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D156">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4">
-      <c r="A157" t="s">
-        <v>157</v>
-      </c>
-      <c r="B157" t="s">
-        <v>0</v>
-      </c>
-      <c r="C157" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D157">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4">
-      <c r="A158" t="s">
-        <v>158</v>
-      </c>
-      <c r="B158" t="s">
-        <v>0</v>
-      </c>
-      <c r="C158" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D158">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4">
-      <c r="A159" t="s">
-        <v>159</v>
-      </c>
-      <c r="B159" t="s">
-        <v>0</v>
-      </c>
-      <c r="C159" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D159">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4">
-      <c r="A160" t="s">
-        <v>160</v>
-      </c>
-      <c r="B160" t="s">
-        <v>0</v>
-      </c>
-      <c r="C160" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D160">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4">
-      <c r="A161" t="s">
-        <v>161</v>
-      </c>
-      <c r="B161" t="s">
-        <v>0</v>
-      </c>
-      <c r="C161" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D161">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4">
-      <c r="A162" t="s">
-        <v>162</v>
-      </c>
-      <c r="B162" t="s">
-        <v>0</v>
-      </c>
-      <c r="C162" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D162">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4">
-      <c r="A163" t="s">
-        <v>163</v>
-      </c>
-      <c r="B163" t="s">
-        <v>0</v>
-      </c>
-      <c r="C163" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D163">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4">
-      <c r="A164" t="s">
-        <v>164</v>
-      </c>
-      <c r="B164" t="s">
-        <v>0</v>
-      </c>
-      <c r="C164" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D164">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4">
-      <c r="A165" t="s">
-        <v>165</v>
-      </c>
-      <c r="B165" t="s">
-        <v>0</v>
-      </c>
-      <c r="C165" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D165">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4">
-      <c r="A166" t="s">
-        <v>166</v>
-      </c>
-      <c r="B166" t="s">
-        <v>0</v>
-      </c>
-      <c r="C166" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D166">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4">
-      <c r="A167" t="s">
-        <v>167</v>
-      </c>
-      <c r="B167" t="s">
-        <v>0</v>
-      </c>
-      <c r="C167" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D167">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4">
-      <c r="A168" t="s">
-        <v>168</v>
-      </c>
-      <c r="B168" t="s">
-        <v>0</v>
-      </c>
-      <c r="C168" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D168">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4">
-      <c r="A169" t="s">
-        <v>169</v>
-      </c>
-      <c r="B169" t="s">
-        <v>0</v>
-      </c>
-      <c r="C169" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D169">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4">
-      <c r="A170" t="s">
-        <v>170</v>
-      </c>
-      <c r="B170" t="s">
-        <v>0</v>
-      </c>
-      <c r="C170" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D170">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4">
-      <c r="A171" t="s">
-        <v>171</v>
-      </c>
-      <c r="B171" t="s">
-        <v>0</v>
-      </c>
-      <c r="C171" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D171">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4">
-      <c r="A172" t="s">
-        <v>172</v>
-      </c>
-      <c r="B172" t="s">
-        <v>0</v>
-      </c>
-      <c r="C172" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D172">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4">
-      <c r="A173" t="s">
-        <v>173</v>
-      </c>
-      <c r="B173" t="s">
-        <v>0</v>
-      </c>
-      <c r="C173" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D173">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4">
-      <c r="A174" t="s">
-        <v>174</v>
-      </c>
-      <c r="B174" t="s">
-        <v>0</v>
-      </c>
-      <c r="C174" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D174">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4">
-      <c r="A175" t="s">
-        <v>175</v>
-      </c>
-      <c r="B175" t="s">
-        <v>0</v>
-      </c>
-      <c r="C175" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D175">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4">
-      <c r="A176" t="s">
-        <v>176</v>
-      </c>
-      <c r="B176" t="s">
-        <v>0</v>
-      </c>
-      <c r="C176" s="1">
-        <v>184.24</v>
-      </c>
-      <c r="D176">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4">
-      <c r="A177" t="s">
-        <v>177</v>
-      </c>
-      <c r="B177" t="s">
-        <v>0</v>
-      </c>
-      <c r="C177" s="1">
-        <v>186.24</v>
-      </c>
-      <c r="D177">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4">
-      <c r="A178" t="s">
-        <v>178</v>
-      </c>
-      <c r="B178" t="s">
-        <v>0</v>
-      </c>
-      <c r="C178" s="1">
-        <v>67.239999999999995</v>
-      </c>
-      <c r="D178">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4">
-      <c r="A179" t="s">
-        <v>179</v>
-      </c>
-      <c r="B179" t="s">
-        <v>0</v>
-      </c>
-      <c r="C179" s="1">
-        <v>194.76</v>
-      </c>
-      <c r="D179">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4">
-      <c r="A180" t="s">
-        <v>180</v>
-      </c>
-      <c r="B180" t="s">
-        <v>0</v>
-      </c>
-      <c r="C180" s="1">
-        <v>128.76</v>
-      </c>
-      <c r="D180">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4">
-      <c r="A181" t="s">
-        <v>181</v>
-      </c>
-      <c r="B181" t="s">
-        <v>0</v>
-      </c>
-      <c r="C181" s="1">
-        <v>194.76</v>
-      </c>
-      <c r="D181">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4">
-      <c r="A182" t="s">
-        <v>182</v>
-      </c>
-      <c r="B182" t="s">
-        <v>0</v>
-      </c>
-      <c r="C182" s="1">
-        <v>146.76</v>
-      </c>
-      <c r="D182">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4">
-      <c r="A183" t="s">
-        <v>183</v>
-      </c>
-      <c r="B183" t="s">
-        <v>0</v>
-      </c>
-      <c r="C183" s="1">
-        <v>138.76</v>
-      </c>
-      <c r="D183">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4">
-      <c r="A184" t="s">
-        <v>184</v>
-      </c>
-      <c r="B184" t="s">
-        <v>0</v>
-      </c>
-      <c r="C184" s="1">
-        <v>116.24</v>
-      </c>
-      <c r="D184">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4">
-      <c r="A185" t="s">
-        <v>185</v>
-      </c>
-      <c r="B185" t="s">
-        <v>0</v>
-      </c>
-      <c r="C185" s="1">
-        <v>109.76</v>
-      </c>
-      <c r="D185">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4">
-      <c r="A186" t="s">
-        <v>186</v>
-      </c>
-      <c r="B186" t="s">
-        <v>0</v>
-      </c>
-      <c r="C186" s="1">
-        <v>65.239999999999995</v>
-      </c>
-      <c r="D186">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4">
-      <c r="A187" t="s">
-        <v>187</v>
-      </c>
-      <c r="B187" t="s">
-        <v>0</v>
-      </c>
-      <c r="C187" s="1">
-        <v>122.76</v>
-      </c>
-      <c r="D187">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4">
-      <c r="A188" t="s">
-        <v>188</v>
-      </c>
-      <c r="B188" t="s">
-        <v>0</v>
-      </c>
-      <c r="C188" s="1">
-        <v>218.76</v>
-      </c>
-      <c r="D188">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4">
-      <c r="A189" t="s">
-        <v>189</v>
-      </c>
-      <c r="B189" t="s">
-        <v>0</v>
-      </c>
-      <c r="C189" s="1">
-        <v>131.24</v>
-      </c>
-      <c r="D189">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4">
-      <c r="A190" t="s">
-        <v>190</v>
-      </c>
-      <c r="B190" t="s">
-        <v>0</v>
-      </c>
-      <c r="C190" s="1">
-        <v>159.24</v>
-      </c>
-      <c r="D190">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4">
-      <c r="A191" t="s">
-        <v>191</v>
-      </c>
-      <c r="B191" t="s">
-        <v>0</v>
-      </c>
-      <c r="C191" s="1">
-        <v>19.82</v>
-      </c>
-      <c r="D191">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4">
-      <c r="A192" t="s">
-        <v>192</v>
-      </c>
-      <c r="B192" t="s">
-        <v>0</v>
-      </c>
-      <c r="C192" s="1">
-        <v>17.7</v>
-      </c>
-      <c r="D192">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4">
-      <c r="A193" t="s">
-        <v>193</v>
-      </c>
-      <c r="B193" t="s">
-        <v>0</v>
-      </c>
-      <c r="C193" s="1">
-        <v>18.38</v>
-      </c>
-      <c r="D193">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4">
-      <c r="A194" t="s">
-        <v>194</v>
-      </c>
-      <c r="B194" t="s">
-        <v>0</v>
-      </c>
-      <c r="C194" s="1">
-        <v>38.76</v>
-      </c>
-      <c r="D194">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4">
-      <c r="A195" t="s">
-        <v>195</v>
-      </c>
-      <c r="B195" t="s">
-        <v>0</v>
-      </c>
-      <c r="C195" s="1">
-        <v>26.24</v>
-      </c>
-      <c r="D195">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4">
-      <c r="A196" t="s">
-        <v>196</v>
-      </c>
-      <c r="B196" t="s">
-        <v>0</v>
-      </c>
-      <c r="C196" s="1">
-        <v>26.24</v>
-      </c>
-      <c r="D196">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4">
-      <c r="A197" t="s">
-        <v>197</v>
-      </c>
-      <c r="B197" t="s">
-        <v>0</v>
-      </c>
-      <c r="C197" s="1">
-        <v>26.24</v>
-      </c>
-      <c r="D197">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4">
-      <c r="A198" t="s">
-        <v>198</v>
-      </c>
-      <c r="B198" t="s">
-        <v>0</v>
-      </c>
-      <c r="C198" s="1">
-        <v>26.24</v>
-      </c>
-      <c r="D198">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4">
-      <c r="A199" t="s">
-        <v>199</v>
-      </c>
-      <c r="B199" t="s">
-        <v>0</v>
-      </c>
-      <c r="C199" s="1">
-        <v>26.24</v>
-      </c>
-      <c r="D199">
-        <v>3.5000000000000003E-2</v>
+      <c r="C155">
+        <v>99.07</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -4867,13 +4125,87 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2243FB5B-7C60-45E4-AB4B-A675DFD3A0E1}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A2:A25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="1:1">
+      <c r="A2" s="1"/>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1"/>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1"/>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1"/>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1"/>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1"/>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1"/>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1"/>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="1"/>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1"/>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1"/>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1"/>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="1"/>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1"/>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1"/>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1"/>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1"/>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1"/>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="1"/>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1"/>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1"/>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>